--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N146_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N146_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.35637450698378</v>
+        <v>5.095410857384865</v>
       </c>
       <c r="D2" t="n">
-        <v>24.40017619461093</v>
+        <v>3.965028631624277</v>
       </c>
       <c r="E2" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F2" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.38816234075853</v>
+        <v>8.513076380373262</v>
       </c>
       <c r="D3" t="n">
-        <v>49.44866928884779</v>
+        <v>8.035408759437766</v>
       </c>
       <c r="E3" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F3" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.074995092263708</v>
+        <v>1.149686702492853</v>
       </c>
       <c r="D4" t="n">
-        <v>18.82817038376273</v>
+        <v>3.059577687361444</v>
       </c>
       <c r="E4" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F4" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.53682040435466</v>
+        <v>3.987233315707633</v>
       </c>
       <c r="D5" t="n">
-        <v>17.21917535772256</v>
+        <v>2.798115995629916</v>
       </c>
       <c r="E5" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F5" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>55.47737676779708</v>
+        <v>9.015073724767024</v>
       </c>
       <c r="D6" t="n">
-        <v>53.95600059307584</v>
+        <v>8.767850096374824</v>
       </c>
       <c r="E6" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F6" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.33478909279786</v>
+        <v>7.366903227579653</v>
       </c>
       <c r="D7" t="n">
-        <v>45.16566798519848</v>
+        <v>7.339421047594754</v>
       </c>
       <c r="E7" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F7" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.16736787588534</v>
+        <v>6.852197279831368</v>
       </c>
       <c r="D8" t="n">
-        <v>36.4797294556446</v>
+        <v>5.927956036542248</v>
       </c>
       <c r="E8" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F8" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>52.74591784556337</v>
+        <v>8.571211649904047</v>
       </c>
       <c r="D9" t="n">
-        <v>51.74252974393884</v>
+        <v>8.408161083390061</v>
       </c>
       <c r="E9" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F9" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>13.31630444749543</v>
+        <v>2.163899472718007</v>
       </c>
       <c r="D10" t="n">
-        <v>13.27250587631546</v>
+        <v>2.156782204901263</v>
       </c>
       <c r="E10" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F10" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.63866848463933</v>
+        <v>5.791283628753891</v>
       </c>
       <c r="D11" t="n">
-        <v>25.64216568773053</v>
+        <v>4.166851924256211</v>
       </c>
       <c r="E11" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F11" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.9851297462914</v>
+        <v>7.472583583772352</v>
       </c>
       <c r="D12" t="n">
-        <v>36.0218278849006</v>
+        <v>5.853547031296348</v>
       </c>
       <c r="E12" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F12" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.42833485549553</v>
+        <v>5.594604414018024</v>
       </c>
       <c r="D13" t="n">
-        <v>32.04294535900358</v>
+        <v>5.206978620838083</v>
       </c>
       <c r="E13" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F13" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>24.6935159518901</v>
+        <v>4.012696342182142</v>
       </c>
       <c r="D14" t="n">
-        <v>23.88101540481345</v>
+        <v>3.880665003282186</v>
       </c>
       <c r="E14" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F14" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>61.16125249080713</v>
+        <v>9.938703529756159</v>
       </c>
       <c r="D15" t="n">
-        <v>3.952847075210474</v>
+        <v>0.642337649721702</v>
       </c>
       <c r="E15" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F15" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>32.52371419490922</v>
+        <v>5.285103556672749</v>
       </c>
       <c r="D16" t="n">
-        <v>3.463423162133094</v>
+        <v>0.5628062638466278</v>
       </c>
       <c r="E16" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F16" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>102.0837535832132</v>
+        <v>16.58860995727214</v>
       </c>
       <c r="D17" t="n">
-        <v>47.20066501414759</v>
+        <v>7.670108064798983</v>
       </c>
       <c r="E17" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F17" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>9.329101756203228</v>
+        <v>1.515979035383024</v>
       </c>
       <c r="D18" t="n">
-        <v>25.45519596937591</v>
+        <v>4.136469345023587</v>
       </c>
       <c r="E18" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F18" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>102.0161440337056</v>
+        <v>16.57762340547715</v>
       </c>
       <c r="D19" t="n">
-        <v>51.74768140568423</v>
+        <v>8.408998228423687</v>
       </c>
       <c r="E19" t="n">
-        <v>25.83256055853758</v>
+        <v>4.197791090762356</v>
       </c>
       <c r="F19" t="n">
-        <v>15.88698967543243</v>
+        <v>2.581635822257769</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
